--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportProductTemplate.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Tên sản phẩm</t>
   </si>
@@ -36,15 +36,9 @@
     <t>Khung 2</t>
   </si>
   <si>
-    <t>Chủng loại</t>
-  </si>
-  <si>
     <t>Pcs/SH</t>
   </si>
   <si>
-    <t>Block/SH</t>
-  </si>
-  <si>
     <t>Số lớp</t>
   </si>
   <si>
@@ -58,6 +52,30 @@
   </si>
   <si>
     <t>DANH SÁCH SẢN PHẨM</t>
+  </si>
+  <si>
+    <t>Tên sản phẩm rút gọn</t>
+  </si>
+  <si>
+    <t>Chủng hàng</t>
+  </si>
+  <si>
+    <t>SH/Block</t>
+  </si>
+  <si>
+    <t>RING/JIG</t>
+  </si>
+  <si>
+    <t>Process</t>
+  </si>
+  <si>
+    <t>Khuôn snap</t>
+  </si>
+  <si>
+    <t>Tape dùng chung</t>
+  </si>
+  <si>
+    <t>Loại TAPE</t>
   </si>
 </sst>
 </file>
@@ -412,81 +430,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="25.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.42578125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="13.7109375" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+    </row>
+    <row r="2" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>9</v>
+      <c r="P2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportProductTemplate.xlsx
@@ -30,12 +30,6 @@
     <t>Kích thước</t>
   </si>
   <si>
-    <t>Khung 1</t>
-  </si>
-  <si>
-    <t>Khung 2</t>
-  </si>
-  <si>
     <t>Pcs/SH</t>
   </si>
   <si>
@@ -76,6 +70,12 @@
   </si>
   <si>
     <t>Loại TAPE</t>
+  </si>
+  <si>
+    <t>Line 1</t>
+  </si>
+  <si>
+    <t>Line 2</t>
   </si>
 </sst>
 </file>
@@ -456,7 +456,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -481,7 +481,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -490,46 +490,46 @@
         <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="K2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="N2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportProductTemplate.xlsx
@@ -433,7 +433,7 @@
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.42578125" style="1" customWidth="1"/>
@@ -448,7 +448,7 @@
     <col min="13" max="13" width="13.7109375" style="1" customWidth="1"/>
     <col min="14" max="14" width="11.42578125" style="1" customWidth="1"/>
     <col min="15" max="15" width="12.42578125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="25.42578125" style="1" customWidth="1"/>
     <col min="17" max="17" width="15.85546875" style="1" customWidth="1"/>
     <col min="18" max="18" width="13.7109375" style="1" customWidth="1"/>
     <col min="19" max="16384" width="9.140625" style="1"/>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportProductTemplate.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$2:$Q$2</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -19,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Tên sản phẩm</t>
   </si>
@@ -30,9 +33,6 @@
     <t>Kích thước</t>
   </si>
   <si>
-    <t>Pcs/SH</t>
-  </si>
-  <si>
     <t>Số lớp</t>
   </si>
   <si>
@@ -54,9 +54,6 @@
     <t>Chủng hàng</t>
   </si>
   <si>
-    <t>SH/Block</t>
-  </si>
-  <si>
     <t>RING/JIG</t>
   </si>
   <si>
@@ -69,13 +66,16 @@
     <t>Tape dùng chung</t>
   </si>
   <si>
-    <t>Loại TAPE</t>
-  </si>
-  <si>
-    <t>Line 1</t>
-  </si>
-  <si>
-    <t>Line 2</t>
+    <t>Line</t>
+  </si>
+  <si>
+    <t>Khung</t>
+  </si>
+  <si>
+    <t>Pcs/Block</t>
+  </si>
+  <si>
+    <t>Block</t>
   </si>
 </sst>
 </file>
@@ -430,11 +430,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.85546875" style="1" customWidth="1"/>
@@ -450,13 +450,12 @@
     <col min="15" max="15" width="12.42578125" style="1" customWidth="1"/>
     <col min="16" max="16" width="25.42578125" style="1" customWidth="1"/>
     <col min="17" max="17" width="15.85546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -474,14 +473,13 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
     </row>
-    <row r="2" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -490,51 +488,49 @@
         <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:Q2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportProductTemplate.xlsx
@@ -51,9 +51,6 @@
     <t>Tên sản phẩm rút gọn</t>
   </si>
   <si>
-    <t>Chủng hàng</t>
-  </si>
-  <si>
     <t>RING/JIG</t>
   </si>
   <si>
@@ -76,6 +73,9 @@
   </si>
   <si>
     <t>Block</t>
+  </si>
+  <si>
+    <t>Tên nguyên vật liệu</t>
   </si>
 </sst>
 </file>
@@ -488,43 +488,43 @@
         <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="P2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportProductTemplate.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$2:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$2:$P$2</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Tên sản phẩm</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>Tên sản phẩm rút gọn</t>
-  </si>
-  <si>
-    <t>RING/JIG</t>
   </si>
   <si>
     <t>Process</t>
@@ -430,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" style="1" customWidth="1"/>
@@ -445,15 +442,14 @@
     <col min="10" max="10" width="13.7109375" style="1" customWidth="1"/>
     <col min="11" max="11" width="14.5703125" style="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="25.42578125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="15.85546875" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="11.42578125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="25.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="15.85546875" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -472,9 +468,8 @@
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
     </row>
-    <row r="2" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -488,25 +483,25 @@
         <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>3</v>
@@ -515,22 +510,19 @@
         <v>9</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>12</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q2"/>
+  <autoFilter ref="A2:P2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
